--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487820_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487820_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.0901</v>
+        <v>0.4163</v>
       </c>
       <c r="E2" t="n">
-        <v>1.7422</v>
+        <v>1.4208</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.6521</v>
+        <v>-1.0044</v>
       </c>
       <c r="G2" t="n">
         <v>-1.6967</v>
@@ -610,13 +610,13 @@
         <v>1.4568</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6224</v>
+        <v>-0.0514</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1239</v>
+        <v>-0.1976</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4985</v>
+        <v>0.1462</v>
       </c>
       <c r="V2" t="n">
         <v>0.7076</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0345</v>
+        <v>-1.5259</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.06270000000000001</v>
+        <v>-1.3486</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0282</v>
+        <v>-0.1773</v>
       </c>
       <c r="G3" t="n">
         <v>-1.8325</v>
@@ -688,13 +688,13 @@
         <v>1.4568</v>
       </c>
       <c r="S3" t="n">
-        <v>2.4223</v>
+        <v>0.931</v>
       </c>
       <c r="T3" t="n">
-        <v>1.6831</v>
+        <v>0.3972</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7392</v>
+        <v>0.5337</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. FRANCO GARCIA</t>
+          <t>A. DIAZ FERREIRA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-2.9822</v>
+        <v>-2.9254</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4456</v>
+        <v>-1.8305</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.4278</v>
+        <v>-1.0948</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.4253</v>
+        <v>-3.4324</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.8081</v>
+        <v>-2.4478</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6172</v>
+        <v>-0.9846</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.4576</v>
+        <v>-1.2728</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.3712</v>
+        <v>-1.3904</v>
       </c>
       <c r="L4" t="n">
-        <v>0.9136</v>
+        <v>0.1176</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.9677</v>
+        <v>-2.1596</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4369</v>
+        <v>-1.0574</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.5308</v>
+        <v>-1.1022</v>
       </c>
       <c r="P4" t="n">
-        <v>1.4568</v>
+        <v>1.2487</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.4568</v>
+        <v>1.2487</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3863</v>
+        <v>-0.9716</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2643</v>
+        <v>-0.7877</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.122</v>
+        <v>-0.184</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.6275</v>
+        <v>0.23</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1675</v>
+        <v>0.23</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.795</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. DIAZ FERREIRA</t>
+          <t>S. FRANCO GARCIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-3.3936</v>
+        <v>-2.9463</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.152</v>
+        <v>0.5109</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.2416</v>
+        <v>-3.4572</v>
       </c>
       <c r="G5" t="n">
-        <v>-3.4324</v>
+        <v>-2.4253</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.4478</v>
+        <v>-1.8081</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.9846</v>
+        <v>-0.6172</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.2728</v>
+        <v>-0.4576</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.3904</v>
+        <v>-1.3712</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1176</v>
+        <v>0.9136</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.1596</v>
+        <v>-1.9677</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.0574</v>
+        <v>-0.4369</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.1022</v>
+        <v>-1.5308</v>
       </c>
       <c r="P5" t="n">
-        <v>1.2487</v>
+        <v>1.4568</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.2487</v>
+        <v>1.4568</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.4399</v>
+        <v>-0.3504</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.1091</v>
+        <v>-0.199</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3308</v>
+        <v>-0.1513</v>
       </c>
       <c r="V5" t="n">
-        <v>0.23</v>
+        <v>-1.6275</v>
       </c>
       <c r="W5" t="n">
-        <v>0.23</v>
+        <v>1.1675</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-2.795</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-3.5909</v>
+        <v>-3.1081</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5918</v>
+        <v>0.7223000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>-4.1827</v>
+        <v>-3.8304</v>
       </c>
       <c r="G6" t="n">
         <v>-6.3964</v>
@@ -922,13 +922,13 @@
         <v>1.0406</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.3838</v>
+        <v>-0.901</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.0472</v>
+        <v>-0.9167</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3366</v>
+        <v>0.0157</v>
       </c>
       <c r="V6" t="n">
         <v>3.1488</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. LUIS</t>
+          <t>J. REILLY</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-5.2291</v>
+        <v>-5.068</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.5291</v>
+        <v>-0.3677</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.7</v>
+        <v>-4.7003</v>
       </c>
       <c r="G7" t="n">
-        <v>-4.2811</v>
+        <v>-3.5939</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.7186</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5625</v>
+        <v>-2.6599</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.0072</v>
+        <v>0.4233</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.0856</v>
+        <v>1.234</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0784</v>
+        <v>-0.8107</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.274</v>
+        <v>-4.0172</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.6331</v>
+        <v>-2.168</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6409</v>
+        <v>-1.8492</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2081</v>
+        <v>1.8731</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2081</v>
+        <v>1.8731</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2414</v>
+        <v>-1.0121</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5219</v>
+        <v>-0.791</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7633</v>
+        <v>-0.2211</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.3975</v>
+        <v>-2.3351</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.3975</v>
+        <v>-2.3351</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. REILLY</t>
+          <t>J. LUIS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-5.8364</v>
+        <v>-5.3378</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7544</v>
+        <v>-2.3148</v>
       </c>
       <c r="F8" t="n">
-        <v>-5.082</v>
+        <v>-3.0229</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.5939</v>
+        <v>-4.2811</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.9340000000000001</v>
+        <v>-3.7186</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.6599</v>
+        <v>-0.5625</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4233</v>
+        <v>-2.0072</v>
       </c>
       <c r="K8" t="n">
-        <v>1.234</v>
+        <v>-2.0856</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.8107</v>
+        <v>0.0784</v>
       </c>
       <c r="M8" t="n">
-        <v>-4.0172</v>
+        <v>-2.274</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.168</v>
+        <v>-1.6331</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.8492</v>
+        <v>-0.6409</v>
       </c>
       <c r="P8" t="n">
-        <v>1.8731</v>
+        <v>0.2081</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8731</v>
+        <v>0.2081</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.7805</v>
+        <v>0.1328</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.1777</v>
+        <v>-0.3076</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6028</v>
+        <v>0.4404</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.3351</v>
+        <v>-1.3975</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.3351</v>
+        <v>-1.3975</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-7.7051</v>
+        <v>-7.604</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.7404</v>
+        <v>-3.6099</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.9647</v>
+        <v>-3.994</v>
       </c>
       <c r="G9" t="n">
         <v>-6.8374</v>
@@ -1156,13 +1156,13 @@
         <v>0.8325</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6596</v>
+        <v>-0.5585</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0472</v>
+        <v>-0.9167</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3876</v>
+        <v>0.3582</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-8.8847</v>
+        <v>-8.277200000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>-7.5381</v>
+        <v>-6.8719</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3466</v>
+        <v>-1.4053</v>
       </c>
       <c r="G10" t="n">
         <v>-4.4137</v>
@@ -1234,13 +1234,13 @@
         <v>0.8325</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6635</v>
+        <v>-0.056</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8482</v>
+        <v>-0.1819</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1847</v>
+        <v>0.1259</v>
       </c>
       <c r="V10" t="n">
         <v>-0.4776</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-10.8186</v>
+        <v>-10.3564</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.4499</v>
+        <v>-6.1051</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.3687</v>
+        <v>-4.2512</v>
       </c>
       <c r="G11" t="n">
         <v>-7.648</v>
@@ -1312,13 +1312,13 @@
         <v>1.0406</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9656</v>
+        <v>-0.5034</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9819</v>
+        <v>-0.6372</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0164</v>
+        <v>0.1338</v>
       </c>
       <c r="V11" t="n">
         <v>-0.1238</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-47.38500000000001</v>
+        <v>-46.7328</v>
       </c>
       <c r="E12" t="n">
-        <v>-20.447</v>
+        <v>-19.7945</v>
       </c>
       <c r="F12" t="n">
-        <v>-26.938</v>
+        <v>-26.9378</v>
       </c>
       <c r="G12" t="n">
         <v>-42.5574</v>
@@ -1390,10 +1390,10 @@
         <v>11.4465</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.9931</v>
+        <v>-3.3406</v>
       </c>
       <c r="T12" t="n">
-        <v>-5.1905</v>
+        <v>-4.5382</v>
       </c>
       <c r="U12" t="n">
         <v>1.1975</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>W. LEVEQUE</t>
+          <t>A. LAFUENTE SISO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>9.571199999999999</v>
+        <v>8.4986</v>
       </c>
       <c r="E13" t="n">
-        <v>6.0979</v>
+        <v>5.3586</v>
       </c>
       <c r="F13" t="n">
-        <v>3.4733</v>
+        <v>3.14</v>
       </c>
       <c r="G13" t="n">
-        <v>5.6303</v>
+        <v>6.5942</v>
       </c>
       <c r="H13" t="n">
-        <v>5.716</v>
+        <v>4.3303</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.0857</v>
+        <v>2.2639</v>
       </c>
       <c r="J13" t="n">
-        <v>5.1569</v>
+        <v>5.3902</v>
       </c>
       <c r="K13" t="n">
-        <v>4.9609</v>
+        <v>3.7713</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1959</v>
+        <v>1.6189</v>
       </c>
       <c r="M13" t="n">
-        <v>0.4734</v>
+        <v>1.204</v>
       </c>
       <c r="N13" t="n">
-        <v>0.7551</v>
+        <v>0.5591</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.2817</v>
+        <v>0.645</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q13" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R13" t="n">
-        <v>1.0406</v>
+        <v>0.8325</v>
       </c>
       <c r="S13" t="n">
-        <v>3.7109</v>
+        <v>0.5911</v>
       </c>
       <c r="T13" t="n">
-        <v>1.7517</v>
+        <v>-0.1586</v>
       </c>
       <c r="U13" t="n">
-        <v>1.9593</v>
+        <v>0.7497</v>
       </c>
       <c r="V13" t="n">
-        <v>0.23</v>
+        <v>1.5213</v>
       </c>
       <c r="W13" t="n">
-        <v>0.23</v>
+        <v>1.1675</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>0.3538</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. LAFUENTE SISO</t>
+          <t>W. LEVEQUE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.747</v>
+        <v>7.5704</v>
       </c>
       <c r="E14" t="n">
-        <v>4.9299</v>
+        <v>4.9192</v>
       </c>
       <c r="F14" t="n">
-        <v>2.817</v>
+        <v>2.6512</v>
       </c>
       <c r="G14" t="n">
-        <v>6.5942</v>
+        <v>5.6303</v>
       </c>
       <c r="H14" t="n">
-        <v>4.3303</v>
+        <v>5.716</v>
       </c>
       <c r="I14" t="n">
-        <v>2.2639</v>
+        <v>-0.0857</v>
       </c>
       <c r="J14" t="n">
-        <v>5.3902</v>
+        <v>5.1569</v>
       </c>
       <c r="K14" t="n">
-        <v>3.7713</v>
+        <v>4.9609</v>
       </c>
       <c r="L14" t="n">
-        <v>1.6189</v>
+        <v>0.1959</v>
       </c>
       <c r="M14" t="n">
-        <v>1.204</v>
+        <v>0.4734</v>
       </c>
       <c r="N14" t="n">
-        <v>0.5591</v>
+        <v>0.7551</v>
       </c>
       <c r="O14" t="n">
-        <v>0.645</v>
+        <v>-0.2817</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.2081</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R14" t="n">
-        <v>0.8325</v>
+        <v>1.0406</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1605</v>
+        <v>1.7102</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5872000000000001</v>
+        <v>0.5729</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4267</v>
+        <v>1.1372</v>
       </c>
       <c r="V14" t="n">
-        <v>1.5213</v>
+        <v>0.23</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1675</v>
+        <v>0.23</v>
       </c>
       <c r="X14" t="n">
-        <v>0.3538</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. STRIKKER</t>
+          <t>A. PALAZUELOS PEREZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.6519</v>
+        <v>6.3931</v>
       </c>
       <c r="E15" t="n">
-        <v>7.3473</v>
+        <v>5.1921</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.6954</v>
+        <v>1.201</v>
       </c>
       <c r="G15" t="n">
-        <v>6.6038</v>
+        <v>6.2145</v>
       </c>
       <c r="H15" t="n">
-        <v>4.0109</v>
+        <v>1.2221</v>
       </c>
       <c r="I15" t="n">
-        <v>2.593</v>
+        <v>4.9924</v>
       </c>
       <c r="J15" t="n">
-        <v>5.7917</v>
+        <v>6.2841</v>
       </c>
       <c r="K15" t="n">
-        <v>3.1661</v>
+        <v>1.1897</v>
       </c>
       <c r="L15" t="n">
-        <v>2.6256</v>
+        <v>5.0945</v>
       </c>
       <c r="M15" t="n">
-        <v>0.8122</v>
+        <v>-0.0696</v>
       </c>
       <c r="N15" t="n">
-        <v>0.8448</v>
+        <v>0.0324</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.0326</v>
+        <v>-0.102</v>
       </c>
       <c r="P15" t="n">
-        <v>0.6244</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R15" t="n">
-        <v>0.6244</v>
+        <v>0.8325</v>
       </c>
       <c r="S15" t="n">
-        <v>1.175</v>
+        <v>0.6167</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3882</v>
+        <v>-0.0514</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7869</v>
+        <v>0.6681</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.7513</v>
+        <v>-0.23</v>
       </c>
       <c r="W15" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.9188</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>L. GARCIA PEREZ</t>
+          <t>M. STRIKKER</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.1269</v>
+        <v>6.3686</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3203</v>
+        <v>7.2402</v>
       </c>
       <c r="F16" t="n">
-        <v>3.8066</v>
+        <v>-0.8716</v>
       </c>
       <c r="G16" t="n">
-        <v>3.1465</v>
+        <v>6.6038</v>
       </c>
       <c r="H16" t="n">
-        <v>2.5889</v>
+        <v>4.0109</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5576</v>
+        <v>2.593</v>
       </c>
       <c r="J16" t="n">
-        <v>1.7709</v>
+        <v>5.7917</v>
       </c>
       <c r="K16" t="n">
-        <v>1.0745</v>
+        <v>3.1661</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6964</v>
+        <v>2.6256</v>
       </c>
       <c r="M16" t="n">
-        <v>1.3755</v>
+        <v>0.8122</v>
       </c>
       <c r="N16" t="n">
-        <v>1.5143</v>
+        <v>0.8448</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1388</v>
+        <v>-0.0326</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.2081</v>
+        <v>0.6244</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.8325</v>
+        <v>0.6244</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3134</v>
+        <v>0.8917</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1924</v>
+        <v>0.281</v>
       </c>
       <c r="U16" t="n">
-        <v>1.1209</v>
+        <v>0.6107</v>
       </c>
       <c r="V16" t="n">
-        <v>1.8751</v>
+        <v>-1.7513</v>
       </c>
       <c r="W16" t="n">
-        <v>1.3975</v>
+        <v>1.1675</v>
       </c>
       <c r="X16" t="n">
-        <v>0.4776</v>
+        <v>-2.9188</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. PALAZUELOS PEREZ</t>
+          <t>L. GARCIA PEREZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,40 +1735,40 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.3876</v>
+        <v>5.4032</v>
       </c>
       <c r="E17" t="n">
-        <v>4.6564</v>
+        <v>2.2131</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7313</v>
+        <v>3.19</v>
       </c>
       <c r="G17" t="n">
-        <v>6.2145</v>
+        <v>3.1465</v>
       </c>
       <c r="H17" t="n">
-        <v>1.2221</v>
+        <v>2.5889</v>
       </c>
       <c r="I17" t="n">
-        <v>4.9924</v>
+        <v>0.5576</v>
       </c>
       <c r="J17" t="n">
-        <v>6.2841</v>
+        <v>1.7709</v>
       </c>
       <c r="K17" t="n">
-        <v>1.1897</v>
+        <v>1.0745</v>
       </c>
       <c r="L17" t="n">
-        <v>5.0945</v>
+        <v>0.6964</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.0696</v>
+        <v>1.3755</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0324</v>
+        <v>1.5143</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.102</v>
+        <v>-0.1388</v>
       </c>
       <c r="P17" t="n">
         <v>-0.2081</v>
@@ -1780,22 +1780,22 @@
         <v>0.8325</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3888</v>
+        <v>0.5897</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5872000000000001</v>
+        <v>0.0853</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1984</v>
+        <v>0.5044</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.23</v>
+        <v>1.8751</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.3975</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.23</v>
+        <v>0.4776</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>4.4438</v>
+        <v>3.8581</v>
       </c>
       <c r="E18" t="n">
-        <v>2.2439</v>
+        <v>1.9224</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2</v>
+        <v>1.9357</v>
       </c>
       <c r="G18" t="n">
         <v>4.8523</v>
@@ -1858,13 +1858,13 @@
         <v>1.0406</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5291</v>
+        <v>-0.0566</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1338</v>
+        <v>-0.4553</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6629</v>
+        <v>0.3987</v>
       </c>
       <c r="V18" t="n">
         <v>-0.9376</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. SANTOS RODRÍGUEZ</t>
+          <t>L. PAUL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.9454</v>
+        <v>3.1804</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3933</v>
+        <v>0.7738</v>
       </c>
       <c r="F19" t="n">
-        <v>2.5521</v>
+        <v>2.4065</v>
       </c>
       <c r="G19" t="n">
-        <v>1.989</v>
+        <v>3.9237</v>
       </c>
       <c r="H19" t="n">
-        <v>2.1898</v>
+        <v>-1.094</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2008</v>
+        <v>5.0177</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0704</v>
+        <v>3.132</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6672</v>
+        <v>-1.8449</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5968</v>
+        <v>4.9769</v>
       </c>
       <c r="M19" t="n">
-        <v>1.9186</v>
+        <v>0.7917999999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>1.5226</v>
+        <v>0.7509</v>
       </c>
       <c r="O19" t="n">
-        <v>0.396</v>
+        <v>0.0408</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6244</v>
+        <v>-1.4568</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-3.1218</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6244</v>
+        <v>1.6649</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3321</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3229</v>
+        <v>-0.6338</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0092</v>
+        <v>-0.0502</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.3975</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.3975</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. MAZAIRA GOMEZ</t>
+          <t>J. SANTOS RODRÍGUEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.8028</v>
+        <v>3.1128</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2486</v>
+        <v>0.179</v>
       </c>
       <c r="F20" t="n">
-        <v>2.5542</v>
+        <v>2.9338</v>
       </c>
       <c r="G20" t="n">
-        <v>2.3904</v>
+        <v>1.989</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4629</v>
+        <v>2.1898</v>
       </c>
       <c r="I20" t="n">
-        <v>1.9276</v>
+        <v>-0.2008</v>
       </c>
       <c r="J20" t="n">
-        <v>2.0069</v>
+        <v>0.0704</v>
       </c>
       <c r="K20" t="n">
-        <v>0.4753</v>
+        <v>0.6672</v>
       </c>
       <c r="L20" t="n">
-        <v>1.5316</v>
+        <v>-0.5968</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3835</v>
+        <v>1.9186</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0124</v>
+        <v>1.5226</v>
       </c>
       <c r="O20" t="n">
         <v>0.396</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2081</v>
+        <v>0.6244</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2487</v>
+        <v>0.6244</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2042</v>
+        <v>0.4994</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7177</v>
+        <v>0.1086</v>
       </c>
       <c r="U20" t="n">
-        <v>0.9219000000000001</v>
+        <v>0.3908</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L. PAUL</t>
+          <t>A. MAZAIRA GOMEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>2.3495</v>
+        <v>3.0949</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5595</v>
+        <v>0.5701000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>1.79</v>
+        <v>2.5248</v>
       </c>
       <c r="G21" t="n">
-        <v>3.9237</v>
+        <v>2.3904</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.094</v>
+        <v>0.4629</v>
       </c>
       <c r="I21" t="n">
-        <v>5.0177</v>
+        <v>1.9276</v>
       </c>
       <c r="J21" t="n">
-        <v>3.132</v>
+        <v>2.0069</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.8449</v>
+        <v>0.4753</v>
       </c>
       <c r="L21" t="n">
-        <v>4.9769</v>
+        <v>1.5316</v>
       </c>
       <c r="M21" t="n">
-        <v>0.7917999999999999</v>
+        <v>0.3835</v>
       </c>
       <c r="N21" t="n">
-        <v>0.7509</v>
+        <v>-0.0124</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0408</v>
+        <v>0.396</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.4568</v>
+        <v>0.2081</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.1218</v>
+        <v>-1.0406</v>
       </c>
       <c r="R21" t="n">
-        <v>1.6649</v>
+        <v>1.2487</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.5149</v>
+        <v>0.4963</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8482</v>
+        <v>-0.3962</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6667</v>
+        <v>0.8925999999999999</v>
       </c>
       <c r="V21" t="n">
-        <v>1.3975</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.3975</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5377</v>
+        <v>0.9282</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.163</v>
+        <v>-0.9487</v>
       </c>
       <c r="F22" t="n">
-        <v>1.7007</v>
+        <v>1.8769</v>
       </c>
       <c r="G22" t="n">
         <v>1.6814</v>
@@ -2170,13 +2170,13 @@
         <v>0.4162</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5193</v>
+        <v>-0.1288</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3915</v>
+        <v>-0.1771</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1278</v>
+        <v>0.0483</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.1788</v>
+        <v>-1.0232</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.6961000000000001</v>
+        <v>-0.4818</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.4827</v>
+        <v>-0.5414</v>
       </c>
       <c r="G23" t="n">
         <v>-0.4687</v>
@@ -2248,13 +2248,13 @@
         <v>1.2487</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6883</v>
+        <v>-0.5327</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5872000000000001</v>
+        <v>-0.3729</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1011</v>
+        <v>-0.1598</v>
       </c>
       <c r="V23" t="n">
         <v>-0.23</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>47.38499999999999</v>
+        <v>47.38509999999999</v>
       </c>
       <c r="E24" t="n">
         <v>26.938</v>
       </c>
       <c r="F24" t="n">
-        <v>20.4471</v>
+        <v>20.4469</v>
       </c>
       <c r="G24" t="n">
         <v>42.5574</v>
@@ -2311,7 +2311,7 @@
         <v>8.795300000000001</v>
       </c>
       <c r="N24" t="n">
-        <v>7.5094</v>
+        <v>7.509399999999999</v>
       </c>
       <c r="O24" t="n">
         <v>1.286</v>
@@ -2326,13 +2326,13 @@
         <v>10.406</v>
       </c>
       <c r="S24" t="n">
-        <v>3.992900000000001</v>
+        <v>3.992999999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.1976</v>
+        <v>-1.1975</v>
       </c>
       <c r="U24" t="n">
-        <v>5.190600000000001</v>
+        <v>5.1905</v>
       </c>
       <c r="V24" t="n">
         <v>1.875</v>
